--- a/data/acompanhamento/trilhas/Git Fundamentals.xlsx
+++ b/data/acompanhamento/trilhas/Git Fundamentals.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,20 +446,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>xp_curso</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ordem_para_assistir</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>tipo_trilha</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>data_final_para_assistir</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>obrigatoriedade_curso</t>
         </is>
@@ -476,19 +481,20 @@
           <t>Introduction to Git</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2 hr</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -503,19 +509,20 @@
           <t>Intermediate Git</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2 hr</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -530,19 +537,20 @@
           <t>Advanced Git</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3 hr</t>
-        </is>
+      <c r="C4" t="n">
+        <v>3</v>
       </c>
       <c r="D4" t="n">
+        <v>2950</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
     </row>
